--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,84 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>MARCOS JESUS</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
   </si>
 </sst>
 </file>
@@ -770,7 +848,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -800,6 +878,213 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920111</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920120</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920130</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920134</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920119</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920124</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
   <si>
     <t>Mat</t>
   </si>
@@ -73,6 +73,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -88,6 +94,12 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
@@ -100,7 +112,7 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>VELASCO</t>
   </si>
   <si>
     <t>BRAVO</t>
@@ -112,6 +124,9 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -124,6 +139,12 @@
     <t>MONTIEL</t>
   </si>
   <si>
+    <t>CRISTIAN MANUEL</t>
+  </si>
+  <si>
+    <t>LUZ AMELY</t>
+  </si>
+  <si>
     <t>KAREN ITZEL</t>
   </si>
   <si>
@@ -137,6 +158,12 @@
   </si>
   <si>
     <t>MELANY NARAYANA</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
   </si>
   <si>
     <t>DIANA IRAIS</t>
@@ -848,7 +875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -880,22 +907,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>21330051920341</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -903,22 +930,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920120</v>
+        <v>21330051920348</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -926,16 +953,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920127</v>
+        <v>21330051920111</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -949,16 +976,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920130</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -972,16 +999,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920134</v>
+        <v>21330051920127</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -995,16 +1022,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920117</v>
+        <v>21330051920130</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1013,21 +1040,21 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920119</v>
+        <v>21330051920134</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1036,27 +1063,27 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920124</v>
+        <v>21330051920343</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1064,24 +1091,116 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
+        <v>21330051920149</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920117</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920119</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920124</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
         <v>21330051920133</v>
       </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -73,109 +73,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
+    <t>MONTIEL</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN MANUEL</t>
-  </si>
-  <si>
-    <t>LUZ AMELY</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
+    <t>CESAR DANIEL</t>
   </si>
   <si>
     <t>GAEL</t>
-  </si>
-  <si>
-    <t>MARCOS JESUS</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
   </si>
 </sst>
 </file>
@@ -576,19 +489,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>70.37</v>
+        <v>88.89</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -602,19 +515,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>77.78</v>
+        <v>92.59</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -628,19 +541,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -693,16 +606,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81.48</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -716,16 +632,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>92.59</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -739,16 +658,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -801,19 +723,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>70.37</v>
+        <v>88.89</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -827,19 +749,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>77.78</v>
+        <v>92.59</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -853,19 +775,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +797,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -907,22 +829,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920341</v>
+        <v>21330051920133</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -930,277 +852,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920348</v>
+        <v>21330051920119</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920111</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920120</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920127</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920130</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920134</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920343</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920149</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920117</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920119</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920124</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920133</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,22 +73,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>GAEL</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MELANY NARAYANA</t>
   </si>
 </sst>
 </file>
@@ -489,19 +480,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -541,19 +532,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -606,19 +597,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>81.48</v>
+        <v>92.59</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -658,19 +649,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>71.43000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -723,19 +714,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -775,16 +766,16 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -797,7 +788,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -829,16 +820,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920133</v>
+        <v>21330051920134</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -848,29 +839,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920119</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
@@ -480,19 +480,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -506,19 +506,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -532,19 +532,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -597,19 +597,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -623,19 +623,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -649,19 +649,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -714,19 +714,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -740,19 +740,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -766,10 +766,10 @@
         <v>28</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>4</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>24</v>
@@ -778,7 +778,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +838,7 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -73,10 +73,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
   </si>
   <si>
     <t>MELANY NARAYANA</t>
@@ -788,7 +797,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -820,16 +829,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920134</v>
+        <v>20330051920152</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -838,6 +847,29 @@
         <v>11</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920134</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
